--- a/artfynd/A 42889-2022 artfynd.xlsx
+++ b/artfynd/A 42889-2022 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 42889-2022 artfynd.xlsx
+++ b/artfynd/A 42889-2022 artfynd.xlsx
@@ -803,7 +803,7 @@
         <v>53065815</v>
       </c>
       <c r="B3" t="n">
-        <v>56395</v>
+        <v>57478</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -844,10 +844,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>617164.4714902706</v>
+        <v>617164</v>
       </c>
       <c r="R3" t="n">
-        <v>6954674.736302409</v>
+        <v>6954675</v>
       </c>
       <c r="S3" t="n">
         <v>100</v>
@@ -877,19 +877,9 @@
           <t>2012-07-11</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2012-07-11</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">

--- a/artfynd/A 42889-2022 artfynd.xlsx
+++ b/artfynd/A 42889-2022 artfynd.xlsx
@@ -803,7 +803,7 @@
         <v>53065815</v>
       </c>
       <c r="B3" t="n">
-        <v>57478</v>
+        <v>57481</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>

--- a/artfynd/A 42889-2022 artfynd.xlsx
+++ b/artfynd/A 42889-2022 artfynd.xlsx
@@ -803,7 +803,7 @@
         <v>53065815</v>
       </c>
       <c r="B3" t="n">
-        <v>57481</v>
+        <v>57487</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>

--- a/artfynd/A 42889-2022 artfynd.xlsx
+++ b/artfynd/A 42889-2022 artfynd.xlsx
@@ -803,7 +803,7 @@
         <v>53065815</v>
       </c>
       <c r="B3" t="n">
-        <v>57487</v>
+        <v>57490</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
